--- a/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
+++ b/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="18" uniqueCount="18">
   <si>
     <t>pull_item</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>weighing_approach</t>
+  </si>
+  <si>
+    <t>price-quantity</t>
   </si>
   <si>
     <t>d_thin</t>
@@ -141,10 +144,10 @@
         <v>14</v>
       </c>
       <c r="J1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2">
@@ -172,8 +175,8 @@
       <c r="H2" s="1">
         <v>2</v>
       </c>
-      <c r="I2" s="1">
-        <v>2</v>
+      <c r="I2" t="s">
+        <v>15</v>
       </c>
       <c r="J2" s="1">
         <v>1</v>

--- a/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
+++ b/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
@@ -13,30 +13,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="32" uniqueCount="25">
   <si>
     <t>pull_item</t>
   </si>
   <si>
-    <t>chicken</t>
+    <t>crackers, cookies, buiscuits, chips/curls</t>
+  </si>
+  <si>
+    <t>fresh fish</t>
   </si>
   <si>
     <t>pull_province</t>
   </si>
   <si>
-    <t>NEGROS OCCIDENTAL</t>
+    <t>AKLAN</t>
+  </si>
+  <si>
+    <t>CAPIZ</t>
+  </si>
+  <si>
+    <t>ILOILO</t>
   </si>
   <si>
     <t>pull_municipal_city</t>
   </si>
   <si>
-    <t>LA CASTELLANA</t>
+    <t>BURUANGA</t>
+  </si>
+  <si>
+    <t>PILAR</t>
+  </si>
+  <si>
+    <t>BAROTAC NUEVO</t>
   </si>
   <si>
     <t>harmonized_nsu_unit</t>
   </si>
   <si>
-    <t>bilog</t>
+    <t>putos</t>
+  </si>
+  <si>
+    <t>pieces or units</t>
   </si>
   <si>
     <t>corrected_unit</t>
@@ -49,6 +67,9 @@
   </si>
   <si>
     <t>medium</t>
+  </si>
+  <si>
+    <t>large</t>
   </si>
   <si>
     <t>grams</t>
@@ -112,7 +133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -120,34 +141,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
@@ -155,33 +176,103 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1">
-        <v>774</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1">
+        <v>245</v>
+      </c>
+      <c r="H3" s="1">
         <v>2</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="1">
-        <v>1</v>
-      </c>
-      <c r="K2" s="1">
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="1">
+        <v>449.5</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1">
         <v>1</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
+++ b/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="25" uniqueCount="20">
   <si>
     <t>pull_item</t>
   </si>
@@ -21,9 +21,6 @@
     <t>crackers, cookies, buiscuits, chips/curls</t>
   </si>
   <si>
-    <t>fresh fish</t>
-  </si>
-  <si>
     <t>pull_province</t>
   </si>
   <si>
@@ -33,9 +30,6 @@
     <t>CAPIZ</t>
   </si>
   <si>
-    <t>ILOILO</t>
-  </si>
-  <si>
     <t>pull_municipal_city</t>
   </si>
   <si>
@@ -45,18 +39,12 @@
     <t>PILAR</t>
   </si>
   <si>
-    <t>BAROTAC NUEVO</t>
-  </si>
-  <si>
     <t>harmonized_nsu_unit</t>
   </si>
   <si>
     <t>putos</t>
   </si>
   <si>
-    <t>pieces or units</t>
-  </si>
-  <si>
     <t>corrected_unit</t>
   </si>
   <si>
@@ -67,9 +55,6 @@
   </si>
   <si>
     <t>medium</t>
-  </si>
-  <si>
-    <t>large</t>
   </si>
   <si>
     <t>grams</t>
@@ -133,7 +118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -141,34 +126,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" t="s">
         <v>19</v>
-      </c>
-      <c r="H1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2">
@@ -176,19 +161,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1">
         <v>90</v>
@@ -197,7 +182,7 @@
         <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
@@ -211,19 +196,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1">
         <v>245</v>
@@ -232,47 +217,12 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J3" s="1">
         <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="1">
-        <v>449.5</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1">
         <v>1</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
+++ b/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="18" uniqueCount="18">
   <si>
     <t>pull_item</t>
   </si>
@@ -27,16 +27,10 @@
     <t>AKLAN</t>
   </si>
   <si>
-    <t>CAPIZ</t>
-  </si>
-  <si>
     <t>pull_municipal_city</t>
   </si>
   <si>
     <t>BURUANGA</t>
-  </si>
-  <si>
-    <t>PILAR</t>
   </si>
   <si>
     <t>harmonized_nsu_unit</t>
@@ -118,7 +112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -129,31 +123,31 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" t="s">
-        <v>18</v>
-      </c>
       <c r="K1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2">
@@ -164,16 +158,16 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
       </c>
       <c r="G2" s="1">
         <v>90</v>
@@ -182,7 +176,7 @@
         <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
@@ -191,41 +185,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1">
-        <v>245</v>
-      </c>
-      <c r="H3" s="1">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
+++ b/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20" uniqueCount="20">
   <si>
     <t>pull_item</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>price-quantity</t>
+  </si>
+  <si>
+    <t>fallback_level</t>
+  </si>
+  <si>
+    <t>own cell x size</t>
   </si>
   <si>
     <t>d_thin</t>
@@ -112,7 +118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -147,7 +153,10 @@
         <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="L1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2">
@@ -178,10 +187,13 @@
       <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="1">
         <v>0</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>1</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
+++ b/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23" uniqueCount="23">
   <si>
     <t>pull_item</t>
   </si>
@@ -61,6 +61,15 @@
   </si>
   <si>
     <t>price-quantity</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>Price-quantity based (lower, median, higher price)</t>
+  </si>
+  <si>
+    <t>d_reclassified</t>
   </si>
   <si>
     <t>fallback_level</t>
@@ -118,7 +127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -158,6 +167,12 @@
       <c r="L1" t="s">
         <v>19</v>
       </c>
+      <c r="M1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -193,7 +208,13 @@
       <c r="K2" s="1">
         <v>0</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
         <v>1</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
+++ b/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
@@ -75,7 +75,7 @@
     <t>fallback_level</t>
   </si>
   <si>
-    <t>own cell x size</t>
+    <t>the cell's own weighings</t>
   </si>
   <si>
     <t>d_thin</t>

--- a/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
+++ b/outputs/master_rename_build/tables/ref_nonmonotonic.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="27" uniqueCount="27">
   <si>
     <t>pull_item</t>
   </si>
@@ -57,6 +57,15 @@
     <t>n_g</t>
   </si>
   <si>
+    <t>n_disputed</t>
+  </si>
+  <si>
+    <t>n_flagged</t>
+  </si>
+  <si>
+    <t>n_uncertain</t>
+  </si>
+  <si>
     <t>weighing_approach</t>
   </si>
   <si>
@@ -79,6 +88,9 @@
   </si>
   <si>
     <t>d_thin</t>
+  </si>
+  <si>
+    <t>share_uncertain</t>
   </si>
   <si>
     <t>nonmono</t>
@@ -127,7 +139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -159,19 +171,31 @@
         <v>14</v>
       </c>
       <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" t="s">
-        <v>18</v>
-      </c>
       <c r="L1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>21</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>22</v>
+      </c>
+      <c r="P1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -199,22 +223,34 @@
       <c r="H2" s="1">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
       </c>
       <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="1">
-        <v>0</v>
-      </c>
       <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1">
         <v>1</v>
       </c>
     </row>
